--- a/recursos/comercial/B2B/PILOTO_B2B_TRACKER.xlsx
+++ b/recursos/comercial/B2B/PILOTO_B2B_TRACKER.xlsx
@@ -678,7 +678,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Metas a 60 días: 10 contactadas · 5 reuniones · 3 convenios · 2 reuniones con gerencia · 10 leads · 3 matrículas. Cortes: día 30 y día 60.</t>
+          <t>Cortes (acumulado mínimo) — Día 15: 6 contactadas · 2 reuniones | Día 30: 12 · 5 · 1 convenio | Día 45: 18 · 8 · 2 convenios · 1 plan empresa · 3 leads · 1 matrícula | Día 60: 24 · 10 · 3 convenios · 2 planes empresa · 10 leads · 3 matrículas.</t>
         </is>
       </c>
     </row>
